--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.38247943222901</v>
+        <v>6.562152907737214</v>
       </c>
       <c r="D2" t="n">
-        <v>19.33279901260754</v>
+        <v>3.141579839548726</v>
       </c>
       <c r="E2" t="n">
-        <v>11.6579696381832</v>
+        <v>1.89442006620477</v>
       </c>
       <c r="F2" t="n">
-        <v>8.801919822193057</v>
+        <v>1.430311971106372</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.502136647597681</v>
+        <v>1.219097205234623</v>
       </c>
       <c r="D3" t="n">
-        <v>4.552224132166105</v>
+        <v>0.739736421476992</v>
       </c>
       <c r="E3" t="n">
-        <v>11.6579696381832</v>
+        <v>1.89442006620477</v>
       </c>
       <c r="F3" t="n">
-        <v>8.801919822193057</v>
+        <v>1.430311971106372</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.7147422823284</v>
+        <v>2.553645620878365</v>
       </c>
       <c r="D4" t="n">
-        <v>15.8902485820707</v>
+        <v>2.58216539458649</v>
       </c>
       <c r="E4" t="n">
-        <v>11.6579696381832</v>
+        <v>1.89442006620477</v>
       </c>
       <c r="F4" t="n">
-        <v>8.801919822193057</v>
+        <v>1.430311971106372</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.30285384653882</v>
+        <v>7.686713750062558</v>
       </c>
       <c r="D5" t="n">
-        <v>30.02861027623816</v>
+        <v>4.879649169888701</v>
       </c>
       <c r="E5" t="n">
-        <v>11.6579696381832</v>
+        <v>1.89442006620477</v>
       </c>
       <c r="F5" t="n">
-        <v>8.801919822193057</v>
+        <v>1.430311971106372</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.13450854386079</v>
+        <v>5.709357638377378</v>
       </c>
       <c r="D6" t="n">
-        <v>27.51817581163403</v>
+        <v>4.471703569390529</v>
       </c>
       <c r="E6" t="n">
-        <v>11.6579696381832</v>
+        <v>1.89442006620477</v>
       </c>
       <c r="F6" t="n">
-        <v>8.801919822193057</v>
+        <v>1.430311971106372</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.58423030816968</v>
+        <v>3.832437425077572</v>
       </c>
       <c r="D7" t="n">
-        <v>22.26800044972188</v>
+        <v>3.618550073079805</v>
       </c>
       <c r="E7" t="n">
-        <v>11.6579696381832</v>
+        <v>1.89442006620477</v>
       </c>
       <c r="F7" t="n">
-        <v>8.801919822193057</v>
+        <v>1.430311971106372</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.78321627981141</v>
+        <v>2.077272645469354</v>
       </c>
       <c r="D8" t="n">
-        <v>13.56572122317657</v>
+        <v>2.204429698766192</v>
       </c>
       <c r="E8" t="n">
-        <v>11.6579696381832</v>
+        <v>1.89442006620477</v>
       </c>
       <c r="F8" t="n">
-        <v>8.801919822193057</v>
+        <v>1.430311971106372</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.45836201376335</v>
+        <v>4.624483827236545</v>
       </c>
       <c r="D9" t="n">
-        <v>29.15628138910079</v>
+        <v>4.737895725728878</v>
       </c>
       <c r="E9" t="n">
-        <v>11.6579696381832</v>
+        <v>1.89442006620477</v>
       </c>
       <c r="F9" t="n">
-        <v>8.801919822193057</v>
+        <v>1.430311971106372</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.49161272623104</v>
+        <v>5.604887068012544</v>
       </c>
       <c r="D10" t="n">
-        <v>35.02745683201954</v>
+        <v>5.691961735203175</v>
       </c>
       <c r="E10" t="n">
-        <v>11.6579696381832</v>
+        <v>1.89442006620477</v>
       </c>
       <c r="F10" t="n">
-        <v>8.801919822193057</v>
+        <v>1.430311971106372</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.31205019212911</v>
+        <v>3.13820815622098</v>
       </c>
       <c r="D11" t="n">
-        <v>19.54570701888259</v>
+        <v>3.176177390568421</v>
       </c>
       <c r="E11" t="n">
-        <v>11.6579696381832</v>
+        <v>1.89442006620477</v>
       </c>
       <c r="F11" t="n">
-        <v>8.801919822193057</v>
+        <v>1.430311971106372</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.83615470998837</v>
+        <v>4.523375140373111</v>
       </c>
       <c r="D12" t="n">
-        <v>10.62641204601029</v>
+        <v>1.726791957476672</v>
       </c>
       <c r="E12" t="n">
-        <v>11.6579696381832</v>
+        <v>1.89442006620477</v>
       </c>
       <c r="F12" t="n">
-        <v>8.801919822193057</v>
+        <v>1.430311971106372</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
